--- a/output/pdf_financials_xlsx/MEGA.xlsx
+++ b/output/pdf_financials_xlsx/MEGA.xlsx
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.766137</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.781778</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.781778</v>
       </c>
     </row>
     <row r="93">
@@ -2338,10 +2338,10 @@
         <v>0.687759</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.9231780000000001</v>
+        <v>0.826704</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>3.05725</v>
+        <v>3.048136</v>
       </c>
     </row>
     <row r="119">
@@ -3001,7 +3001,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3278,7 +3282,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>1.766137</v>
       </c>
@@ -3830,7 +3838,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MEGA.xlsx
+++ b/output/pdf_financials_xlsx/MEGA.xlsx
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.0007470000000000001</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -864,7 +864,7 @@
         <v>-1.106498</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.984261</v>
+        <v>-1.985008</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-3.48896</v>
@@ -896,7 +896,7 @@
         <v>-1.106498</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.984261</v>
+        <v>-1.985008</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-3.48896</v>
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.036715</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.046431</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000522</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.036715</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.046431</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000522</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.206954</v>
+        <v>0.170239</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.09467200000000001</v>
+        <v>0.048241</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.02057</v>
+        <v>0.020048</v>
       </c>
     </row>
     <row r="49">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">

--- a/output/pdf_financials_xlsx/MEGA.xlsx
+++ b/output/pdf_financials_xlsx/MEGA.xlsx
@@ -2066,10 +2066,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.109691</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.008433</v>
       </c>
     </row>
     <row r="102">
@@ -2146,10 +2146,10 @@
         <v>-0.166043</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.7486120000000001</v>
+        <v>0.858303</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.356291</v>
+        <v>0.364724</v>
       </c>
     </row>
     <row r="107">
@@ -3623,7 +3623,11 @@
           <t>Recovery of provision for uncollectible GST recoverable</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -3654,7 +3658,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
